--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1605,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106663525</v>
+        <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>56830</v>
+        <v>58005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,58 +1616,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100092</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräknesbacken, Hl</t>
+          <t>Berget, Ullasjö, Enslöv, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>384347</v>
+        <v>384401</v>
       </c>
       <c r="R10" t="n">
-        <v>6295483</v>
+        <v>6295472</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,22 +1674,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,35 +1691,20 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Autoboxlokal</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Martin Brüsin</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Alexander Eriksson</t>
-        </is>
-      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106663525</t>
+          <t>https://artportalen.se/Sighting/137138112</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119586841</v>
+        <v>106663525</v>
       </c>
       <c r="B11" t="n">
-        <v>44177</v>
+        <v>56830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,37 +1712,58 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Berget/Spjutaberget, Hl</t>
+          <t>Bräknesbacken, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>384463</v>
+        <v>384347</v>
       </c>
       <c r="R11" t="n">
-        <v>6295391</v>
+        <v>6295483</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1808,12 +1787,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,42 +1814,32 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Celander</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119586841</t>
+          <t>https://artportalen.se/Sighting/106663525</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119586864</v>
+        <v>119586841</v>
       </c>
       <c r="B12" t="n">
         <v>44177</v>
@@ -1895,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>384386</v>
+        <v>384463</v>
       </c>
       <c r="R12" t="n">
-        <v>6295471</v>
+        <v>6295391</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1971,16 +1950,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119586864</t>
+          <t>https://artportalen.se/Sighting/119586841</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106664909</v>
+        <v>119586864</v>
       </c>
       <c r="B13" t="n">
-        <v>56823</v>
+        <v>44177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,58 +1967,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205992</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>detektor med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bräknesbacken, Hl</t>
+          <t>Berget/Spjutaberget, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>384347</v>
+        <v>384386</v>
       </c>
       <c r="R13" t="n">
-        <v>6295483</v>
+        <v>6295471</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2063,22 +2021,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,35 +2038,45 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Autoboxlokal</t>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Patrik Celander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106664909</t>
+          <t>https://artportalen.se/Sighting/119586864</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106660533</v>
+        <v>106664909</v>
       </c>
       <c r="B14" t="n">
-        <v>56835</v>
+        <v>56823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,26 +2084,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2247,43 +2205,43 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106660533</t>
+          <t>https://artportalen.se/Sighting/106664909</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106662054</v>
+        <v>106660533</v>
       </c>
       <c r="B15" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2384,6 +2342,144 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106660533</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>106662054</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bräknesbacken, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>384347</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6295483</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Autoboxlokal</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/106662054</t>
         </is>
@@ -2405,6 +2501,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1692,6 +1692,16 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tommy Levin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Levin</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49151-2024 artfynd.xlsx
+++ b/artfynd/A 49151-2024 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>137138112</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
